--- a/output/第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx
+++ b/output/第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>3町への照会。見える化システムのF15〜F25（地域ケア会議開催回数を含む）は再出力を依頼中</t>
+          <t>3町への照会。見える化システムのF15〜F25（地域ケア会議開催回数を含む）は再出力を依頼中。令和8年9月25日受領の3町の地域包括支援センター事業実施報告書により、美瑛町の令和7年度は年6回（隔月1回）、令和8年度計画は年12回（毎月1回）と分かった。東川町は生活支援体制整備事業の中で「地域ケア会議、個別会議への参加12回」と報告している。東神楽町は量の欄が人数であり回数が分からない。3町で単位がそろっていないため合計できない</t>
         </is>
       </c>
     </row>
